--- a/review-tasks/1d-python-review/participant/answer-template.xlsx
+++ b/review-tasks/1d-python-review/participant/answer-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1d-python-review/participant/answer-template.xlsx
+++ b/review-tasks/1d-python-review/participant/answer-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1d-python-review/participant/answer-template.xlsx
+++ b/review-tasks/1d-python-review/participant/answer-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ответ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,14 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,17 +446,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Что не так</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Почему это проблема</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Как исправить</t>
+          <t>Замечание</t>
         </is>
       </c>
     </row>
@@ -470,8 +458,6 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,8 +467,6 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -492,8 +476,6 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,8 +485,6 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -514,8 +494,6 @@
       </c>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -525,8 +503,6 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -536,8 +512,6 @@
       </c>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -547,8 +521,6 @@
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -558,8 +530,6 @@
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -569,8 +539,6 @@
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -580,8 +548,6 @@
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -591,8 +557,6 @@
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -602,8 +566,6 @@
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,8 +575,6 @@
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -624,8 +584,6 @@
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -635,8 +593,6 @@
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -646,8 +602,6 @@
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -657,8 +611,6 @@
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -668,8 +620,6 @@
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -679,8 +629,6 @@
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -690,8 +638,6 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -701,8 +647,6 @@
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -712,8 +656,6 @@
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -723,8 +665,6 @@
       </c>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -734,8 +674,6 @@
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -745,8 +683,6 @@
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -756,8 +692,6 @@
       </c>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -767,8 +701,6 @@
       </c>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -778,8 +710,6 @@
       </c>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -789,8 +719,6 @@
       </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -800,8 +728,6 @@
       </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -811,8 +737,6 @@
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -822,8 +746,6 @@
       </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -833,8 +755,6 @@
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -844,8 +764,6 @@
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -855,8 +773,6 @@
       </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,8 +782,6 @@
       </c>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -877,8 +791,6 @@
       </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -888,8 +800,6 @@
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -899,8 +809,6 @@
       </c>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -910,8 +818,6 @@
       </c>
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -921,8 +827,6 @@
       </c>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -932,8 +836,6 @@
       </c>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -943,8 +845,6 @@
       </c>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -954,8 +854,6 @@
       </c>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -965,8 +863,6 @@
       </c>
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -976,8 +872,6 @@
       </c>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -987,8 +881,6 @@
       </c>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -998,8 +890,6 @@
       </c>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1009,8 +899,6 @@
       </c>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1020,8 +908,6 @@
       </c>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1031,8 +917,6 @@
       </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1042,8 +926,6 @@
       </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1053,8 +935,6 @@
       </c>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1064,8 +944,6 @@
       </c>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1075,8 +953,6 @@
       </c>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1086,8 +962,6 @@
       </c>
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1097,8 +971,6 @@
       </c>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1108,8 +980,6 @@
       </c>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1119,8 +989,6 @@
       </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1130,8 +998,6 @@
       </c>
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1141,8 +1007,6 @@
       </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1152,8 +1016,6 @@
       </c>
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1163,8 +1025,6 @@
       </c>
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1174,8 +1034,6 @@
       </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1185,8 +1043,6 @@
       </c>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1196,8 +1052,6 @@
       </c>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1207,8 +1061,6 @@
       </c>
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1218,8 +1070,6 @@
       </c>
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1229,8 +1079,6 @@
       </c>
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1240,8 +1088,6 @@
       </c>
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1251,8 +1097,6 @@
       </c>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1262,8 +1106,6 @@
       </c>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1273,8 +1115,6 @@
       </c>
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1284,8 +1124,6 @@
       </c>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1295,8 +1133,6 @@
       </c>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1306,8 +1142,6 @@
       </c>
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1317,8 +1151,6 @@
       </c>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1328,8 +1160,6 @@
       </c>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1339,8 +1169,6 @@
       </c>
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1350,8 +1178,6 @@
       </c>
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1361,8 +1187,6 @@
       </c>
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1372,8 +1196,6 @@
       </c>
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1383,8 +1205,6 @@
       </c>
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1394,8 +1214,6 @@
       </c>
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1405,8 +1223,6 @@
       </c>
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1416,8 +1232,6 @@
       </c>
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1427,8 +1241,6 @@
       </c>
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1438,8 +1250,6 @@
       </c>
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1449,8 +1259,6 @@
       </c>
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1460,8 +1268,6 @@
       </c>
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1471,8 +1277,6 @@
       </c>
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1482,8 +1286,6 @@
       </c>
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1493,8 +1295,6 @@
       </c>
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1504,8 +1304,6 @@
       </c>
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1515,8 +1313,6 @@
       </c>
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1526,8 +1322,6 @@
       </c>
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1537,8 +1331,6 @@
       </c>
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1548,8 +1340,6 @@
       </c>
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1559,8 +1349,6 @@
       </c>
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
